--- a/raw/DB/TheVenti.xlsx
+++ b/raw/DB/TheVenti.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\기타서류\3.홈페이지 아이디어\DB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6f05ca6d36262a21/Desktop/caffeinenote/raw/DB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68761416-8E3A-4916-A53D-F898F9479350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{68761416-8E3A-4916-A53D-F898F9479350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54963F65-D6F1-4C63-B2FF-2AA7905D27AD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="16200" windowHeight="9307" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="더벤티" sheetId="1" r:id="rId1"/>
     <sheet name="출처" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">더벤티!$A$1:$H$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">더벤티!$A$1:$H$291</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="348">
   <si>
     <t>분류</t>
   </si>
@@ -10452,30 +10452,6 @@
       </rPr>
       <t>)</t>
     </r>
-  </si>
-  <si>
-    <t>사이드메뉴</t>
-  </si>
-  <si>
-    <t>분식</t>
-  </si>
-  <si>
-    <t>벤티네 로제 떡볶이</t>
-  </si>
-  <si>
-    <t>360g</t>
-  </si>
-  <si>
-    <t>벤티네 마라 떡볶이</t>
-  </si>
-  <si>
-    <t>벤티네 매콤 소보로밥</t>
-  </si>
-  <si>
-    <t>100g</t>
-  </si>
-  <si>
-    <t>벤티네 간장 소보로밥</t>
   </si>
   <si>
     <t>설명</t>
@@ -11119,8 +11095,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H295"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <dimension ref="A1:H291"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -18698,112 +18674,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="292" spans="1:8">
-      <c r="A292" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D292" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E292" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="F292" s="4">
-        <v>583.20000000000005</v>
-      </c>
-      <c r="G292" s="4">
-        <v>22</v>
-      </c>
-      <c r="H292" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="1:8">
-      <c r="A293" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D293" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="E293" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="F293" s="4">
-        <v>594</v>
-      </c>
-      <c r="G293" s="4">
-        <v>18</v>
-      </c>
-      <c r="H293" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="1:8">
-      <c r="A294" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D294" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E294" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="F294" s="4">
-        <v>180</v>
-      </c>
-      <c r="G294" s="4">
-        <v>3</v>
-      </c>
-      <c r="H294" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="1:8">
-      <c r="A295" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C295" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D295" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E295" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="F295" s="4">
-        <v>195</v>
-      </c>
-      <c r="G295" s="4">
-        <v>3</v>
-      </c>
-      <c r="H295" s="4">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H295" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H291" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18813,7 +18685,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -18821,42 +18693,42 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="5" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="6" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="6" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="6" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="6" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
